--- a/demo/SimWind/batch_templates/Offshore_WindCases_Generic.xlsx
+++ b/demo/SimWind/batch_templates/Offshore_WindCases_Generic.xlsx
@@ -16,8 +16,15 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dxfs>
+	</dxfs>
   <numFmts count="0"/>
   <fonts count="2">
     <font>
